--- a/tests/fixtures/raw/CP04_unlabeled.xlsx
+++ b/tests/fixtures/raw/CP04_unlabeled.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,11 @@
           <t>적용모델</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>개정일</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -617,6 +622,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="n"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="n"/>
@@ -657,6 +667,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="n"/>
@@ -701,6 +716,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="n"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="n"/>
@@ -737,6 +757,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="n"/>
@@ -781,6 +806,11 @@
         </is>
       </c>
       <c r="J8" s="4" t="n"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -821,6 +851,11 @@
         </is>
       </c>
       <c r="J9" s="4" t="n"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="n"/>
@@ -865,6 +900,11 @@
         </is>
       </c>
       <c r="J10" s="4" t="n"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -909,6 +949,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -953,6 +998,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="n"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="7" t="n"/>
@@ -997,15 +1047,20 @@
         </is>
       </c>
       <c r="J13" s="4" t="n"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A4:A13"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
